--- a/用卷/xlsx/2011.xlsx
+++ b/用卷/xlsx/2011.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184ABABC-427A-43AC-A7A2-D381FA793251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769C604B-8376-4623-95EE-E9FBC5FD408E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,9 +247,6 @@
     <t>文综、理综为新课标卷,其他科目为江西卷</t>
   </si>
   <si>
-    <t>文综、理综为新课标卷,其他科目为湖北卷</t>
-  </si>
-  <si>
     <t>文综、理综为新课标卷,其他科目为湖南卷</t>
   </si>
   <si>
@@ -304,6 +301,10 @@
   </si>
   <si>
     <t>英语笔试分数乘7/6+听力分数/3四舍五入等于总成绩</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>文综、理综为大纲卷,其他科目为湖北卷</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -843,7 +844,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -851,7 +852,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -919,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -945,7 +946,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>52</v>
@@ -959,7 +960,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>52</v>
@@ -976,7 +977,7 @@
         <v>70</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1094,8 +1095,8 @@
       <c r="B21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>72</v>
+      <c r="C21" s="16" t="s">
+        <v>86</v>
       </c>
       <c r="D21" s="1"/>
     </row>
@@ -1107,7 +1108,7 @@
         <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D22" s="1"/>
     </row>
@@ -1122,7 +1123,7 @@
         <v>61</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -1133,7 +1134,7 @@
         <v>27</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D24" s="1"/>
     </row>
@@ -1145,7 +1146,7 @@
         <v>28</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="1"/>
     </row>
@@ -1183,7 +1184,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D28" s="6"/>
     </row>
@@ -1195,7 +1196,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>64</v>
@@ -1209,7 +1210,7 @@
         <v>33</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30" s="1"/>
     </row>
@@ -1221,7 +1222,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>62</v>
@@ -1235,7 +1236,7 @@
         <v>35</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D32" s="3"/>
     </row>
@@ -1247,7 +1248,7 @@
         <v>36</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D33" s="1"/>
     </row>
@@ -1309,7 +1310,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
@@ -1320,7 +1321,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1331,7 +1332,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1342,7 +1343,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1353,7 +1354,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1364,7 +1365,7 @@
         <v>14</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1375,7 +1376,7 @@
         <v>14</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1386,7 +1387,7 @@
         <v>14</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1397,7 +1398,7 @@
         <v>14</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
